--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488288_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488288_PROCESSED_CHRONO.xlsx
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VAZQUEZ SUAREZ</t>
+          <t>J. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6952</v>
+        <v>2.5353</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4325</v>
+        <v>5.1921</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7373</v>
+        <v>-2.6568</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0078</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8153</v>
+        <v>-2.767</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8231</v>
+        <v>2.2271</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1095</v>
+        <v>2.3664</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8346</v>
+        <v>-0.8897</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7251</v>
+        <v>3.2561</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.1174</v>
+        <v>-2.9063</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0194</v>
+        <v>-1.8773</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.098</v>
+        <v>-1.029</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8529</v>
+        <v>0.9264</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0665</v>
+        <v>0.4309</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9176</v>
+        <v>0.605</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8511</v>
+        <v>-0.1741</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6366</v>
+        <v>2.6442</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2583</v>
+        <v>3.1471</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3783</v>
+        <v>-0.5029</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. PINA FURTADO</t>
+          <t>J. VAZQUEZ SUAREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6814</v>
+        <v>1.9173</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8756</v>
+        <v>3.7038</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.1942</v>
+        <v>-1.7865</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6127</v>
+        <v>-0.0078</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06619999999999999</v>
+        <v>1.8153</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5466</v>
+        <v>-1.8231</v>
       </c>
       <c r="J4" t="n">
-        <v>6.508</v>
+        <v>3.1095</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4947</v>
+        <v>3.8346</v>
       </c>
       <c r="L4" t="n">
-        <v>4.0133</v>
+        <v>-0.7251</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.8952</v>
+        <v>-3.1174</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.4285</v>
+        <v>-2.0194</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4667</v>
+        <v>-1.098</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.6676</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1117</v>
+        <v>1.8529</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5552</v>
+        <v>0.2885</v>
       </c>
       <c r="T4" t="n">
-        <v>1.833</v>
+        <v>1.1889</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2778</v>
+        <v>-0.9004</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.819</v>
+        <v>1.6366</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3139</v>
+        <v>1.2583</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1329</v>
+        <v>0.3783</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BRAVO ORTEGA</t>
+          <t>A. VEGUILLA SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6714</v>
+        <v>1.3141</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5498</v>
+        <v>4.701</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8784</v>
+        <v>-3.3869</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5397999999999999</v>
+        <v>2.8311</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.767</v>
+        <v>-1.4943</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2271</v>
+        <v>4.3253</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3664</v>
+        <v>5.0849</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8897</v>
+        <v>0.4294</v>
       </c>
       <c r="L5" t="n">
-        <v>3.2561</v>
+        <v>4.6555</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.9063</v>
+        <v>-2.2538</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8773</v>
+        <v>-1.9237</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.029</v>
+        <v>-0.3301</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.433</v>
+        <v>0.4306</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0373</v>
+        <v>0.5425</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3957</v>
+        <v>-0.1119</v>
       </c>
       <c r="V5" t="n">
-        <v>2.6442</v>
+        <v>-1.7623</v>
       </c>
       <c r="W5" t="n">
-        <v>3.1471</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5029</v>
+        <v>-1.7623</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. VEGUILLA SANCHEZ</t>
+          <t>É. PINA FURTADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3628</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7989</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.4361</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8311</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4943</v>
+        <v>0.3221</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3253</v>
+        <v>0.6221</v>
       </c>
       <c r="J6" t="n">
-        <v>5.0849</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4294</v>
+        <v>0.3221</v>
       </c>
       <c r="L6" t="n">
-        <v>4.6555</v>
+        <v>0.6221</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2538</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9237</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3301</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4793</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6404</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1612</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7623</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7623</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>É. PINA FURTADO</t>
+          <t>E. PINA FURTADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9034</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9441000000000001</v>
+        <v>5.1469</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-4.2434</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9441000000000001</v>
+        <v>2.6127</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3221</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6221</v>
+        <v>2.5466</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9441000000000001</v>
+        <v>6.508</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3221</v>
+        <v>2.4947</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6221</v>
+        <v>4.0133</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-3.8952</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-2.4285</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1.4667</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.7772</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.1043</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.3271</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.819</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3139</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1329</v>
       </c>
     </row>
     <row r="8">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0273</v>
+        <v>-0.2429</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6987</v>
+        <v>0.6008</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6714</v>
+        <v>-0.8437</v>
       </c>
       <c r="G9" t="n">
         <v>0.4087</v>
@@ -1156,13 +1156,13 @@
         <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2557</v>
+        <v>-0.0146</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2151</v>
+        <v>0.1172</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0405</v>
+        <v>-0.1318</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0076</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7696</v>
+        <v>-0.7647</v>
       </c>
       <c r="E10" t="n">
-        <v>1.013</v>
+        <v>1.1656</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7826</v>
+        <v>-1.9303</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8702</v>
@@ -1234,13 +1234,13 @@
         <v>1.8529</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4362</v>
+        <v>0.4411</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.8951</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3062</v>
+        <v>-0.4539</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1884</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6727</v>
+        <v>-1.427</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2275</v>
+        <v>-1.1296</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4452</v>
+        <v>-0.2974</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0441</v>
@@ -1312,13 +1312,13 @@
         <v>0.1853</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4362</v>
+        <v>-0.1906</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1079</v>
+        <v>0.0398</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3777</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8873</v>
+        <v>-1.9611</v>
       </c>
       <c r="E12" t="n">
         <v>-1.0859</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8014</v>
+        <v>-0.8752</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8183</v>
@@ -1390,13 +1390,13 @@
         <v>0.3706</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1251</v>
+        <v>-0.199</v>
       </c>
       <c r="T12" t="n">
         <v>0.051</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1761</v>
+        <v>-0.25</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3144</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1987</v>
+        <v>-2.5844</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4867</v>
+        <v>-1.9216</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.712</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0719</v>
@@ -1468,13 +1468,13 @@
         <v>0.3706</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7615</v>
+        <v>0.3759</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9774</v>
+        <v>0.5425</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2159</v>
+        <v>-0.1666</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2589</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.1641</v>
+        <v>-2.8457</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.4081</v>
+        <v>-2.1143</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.756</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-1.5152</v>
@@ -1546,13 +1546,13 @@
         <v>0.3706</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4636</v>
+        <v>-0.1452</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2189</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2447</v>
+        <v>-0.2201</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6294</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.0675</v>
+        <v>-3.8962</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.2674</v>
+        <v>-4.0716</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1999</v>
+        <v>0.1753</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6665</v>
@@ -1624,13 +1624,13 @@
         <v>0.7411</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9851</v>
+        <v>-0.8139</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3283</v>
+        <v>-0.1324</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6815</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3777</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-7.9487</v>
+        <v>-6.9447</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.0017</v>
+        <v>-5.0225</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9469</v>
+        <v>-1.9223</v>
       </c>
       <c r="G16" t="n">
         <v>-1.6657</v>
@@ -1702,13 +1702,13 @@
         <v>1.297</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6263</v>
+        <v>-0.6224</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8879</v>
+        <v>0.0914</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7383999999999999</v>
+        <v>-0.7138</v>
       </c>
       <c r="V16" t="n">
         <v>-1.3215</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-9.2498</v>
+        <v>-8.975899999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>9.911900000000005</v>
+        <v>10.1854</v>
       </c>
       <c r="F17" t="n">
-        <v>-19.1616</v>
+        <v>-19.1614</v>
       </c>
       <c r="G17" t="n">
         <v>-1.326300000000001</v>
@@ -1750,7 +1750,7 @@
         <v>-9.197900000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>7.871399999999999</v>
+        <v>7.8714</v>
       </c>
       <c r="J17" t="n">
         <v>15.7548</v>
@@ -1780,19 +1780,19 @@
         <v>10.1908</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4850999999999992</v>
+        <v>0.7585000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>4.576200000000002</v>
+        <v>4.850000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.0913</v>
+        <v>-4.091399999999999</v>
       </c>
       <c r="V17" t="n">
         <v>-3.776099999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>4.4037</v>
+        <v>4.403700000000001</v>
       </c>
       <c r="X17" t="n">
         <v>-8.18</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6.9277</v>
+        <v>8.462999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>7.4645</v>
+        <v>8.541700000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.0786</v>
       </c>
       <c r="G18" t="n">
         <v>2.1495</v>
@@ -1858,13 +1858,13 @@
         <v>2.4087</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5363</v>
+        <v>-0.0009</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7909</v>
+        <v>0.2864</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7454</v>
+        <v>-0.2873</v>
       </c>
       <c r="V18" t="n">
         <v>4.091</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>A. VALDERRAMA VIDAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>6.5301</v>
+        <v>4.8756</v>
       </c>
       <c r="E19" t="n">
-        <v>4.9907</v>
+        <v>2.7715</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5394</v>
+        <v>2.1041</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0386</v>
+        <v>3.2138</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7987</v>
+        <v>-1.084</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.7601</v>
+        <v>4.2978</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7632</v>
+        <v>2.8879</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9031</v>
+        <v>-0.9796</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1398</v>
+        <v>3.8675</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7247</v>
+        <v>0.3259</v>
       </c>
       <c r="N19" t="n">
         <v>-0.1044</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6203</v>
+        <v>0.4303</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1853</v>
+        <v>0.7411</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0382</v>
+        <v>-1.1117</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2234</v>
+        <v>1.8529</v>
       </c>
       <c r="S19" t="n">
-        <v>3.7324</v>
+        <v>0.6062</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6923</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0401</v>
+        <v>-0.0746</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5738</v>
+        <v>0.3144</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5733</v>
+        <v>0.3144</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA VIDAL</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>5.2833</v>
+        <v>4.756</v>
       </c>
       <c r="E20" t="n">
-        <v>3.359</v>
+        <v>3.5217</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9243</v>
+        <v>1.2342</v>
       </c>
       <c r="G20" t="n">
-        <v>3.2138</v>
+        <v>1.0386</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.084</v>
+        <v>3.7987</v>
       </c>
       <c r="I20" t="n">
-        <v>4.2978</v>
+        <v>-2.7601</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8879</v>
+        <v>2.7632</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9796</v>
+        <v>3.9031</v>
       </c>
       <c r="L20" t="n">
-        <v>3.8675</v>
+        <v>-1.1398</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3259</v>
+        <v>-1.7247</v>
       </c>
       <c r="N20" t="n">
         <v>-0.1044</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4303</v>
+        <v>-1.6203</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1117</v>
+        <v>-2.0382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8529</v>
+        <v>2.2234</v>
       </c>
       <c r="S20" t="n">
-        <v>1.014</v>
+        <v>1.9583</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2684</v>
+        <v>1.2234</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2545</v>
+        <v>0.7349</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3144</v>
+        <v>1.5738</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3144</v>
+        <v>1.5733</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. NGOM</t>
+          <t>J. LÓPEZ RUIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.6532</v>
+        <v>1.5883</v>
       </c>
       <c r="E21" t="n">
-        <v>2.4861</v>
+        <v>1.5883</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1671</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5331</v>
+        <v>1.5883</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5513</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0844</v>
+        <v>0.6221</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4641</v>
+        <v>1.5883</v>
       </c>
       <c r="K21" t="n">
-        <v>0.412</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0522</v>
+        <v>0.6221</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9973</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1393</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1366</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.1297</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.022</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1077</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. LÓPEZ RUIZ</t>
+          <t>E. NGOM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5883</v>
+        <v>1.4037</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5883</v>
+        <v>1.4089</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-0.0053</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5883</v>
+        <v>-0.5331</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.5513</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6221</v>
+        <v>-1.0844</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5883</v>
+        <v>0.4641</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.412</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6221</v>
+        <v>0.0522</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>-0.9973</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.1393</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-1.1366</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.8801</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.9448</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>R. ORTEGA MORA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2474</v>
+        <v>0.6032</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6456</v>
+        <v>-0.2819</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.893</v>
+        <v>0.885</v>
       </c>
       <c r="G23" t="n">
-        <v>0.121</v>
+        <v>-0.2598</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2738</v>
+        <v>-0.4027</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3948</v>
+        <v>0.1429</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4866</v>
+        <v>-0.2782</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5455</v>
+        <v>-0.3825</v>
       </c>
       <c r="L23" t="n">
-        <v>2.0321</v>
+        <v>0.1043</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3656</v>
+        <v>0.0183</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.0203</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6373</v>
+        <v>0.0386</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7411</v>
+        <v>1.297</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7411</v>
+        <v>1.4823</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7951</v>
+        <v>-0.434</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.526</v>
+        <v>0.1816</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2691</v>
+        <v>-0.6156</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. ORTEGA MORA</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6063</v>
+        <v>-0.1987</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0653</v>
+        <v>0.7435</v>
       </c>
       <c r="F24" t="n">
-        <v>0.459</v>
+        <v>-0.9422</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2598</v>
+        <v>0.121</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4027</v>
+        <v>-1.2738</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1429</v>
+        <v>1.3948</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2782</v>
+        <v>1.4866</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3825</v>
+        <v>-0.5455</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1043</v>
+        <v>2.0321</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0183</v>
+        <v>-1.3656</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0203</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0386</v>
+        <v>-0.6373</v>
       </c>
       <c r="P24" t="n">
-        <v>1.297</v>
+        <v>0.7411</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4823</v>
+        <v>0.7411</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6435</v>
+        <v>-0.7464</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6019</v>
+        <v>-0.4281</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0416</v>
+        <v>-0.3184</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.644</v>
+        <v>-0.7665</v>
       </c>
       <c r="E25" t="n">
-        <v>0.892</v>
+        <v>0.794</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.536</v>
+        <v>-1.5606</v>
       </c>
       <c r="G25" t="n">
         <v>0.3076</v>
@@ -2404,13 +2404,13 @@
         <v>0.7411</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7663</v>
+        <v>-0.8888</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2151</v>
+        <v>0.1172</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9814000000000001</v>
+        <v>-1.006</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.314</v>
+        <v>-1.2745</v>
       </c>
       <c r="E26" t="n">
         <v>2.3587</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.6728</v>
+        <v>-3.6332</v>
       </c>
       <c r="G26" t="n">
         <v>0.6223</v>
@@ -2482,13 +2482,13 @@
         <v>2.2234</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2323</v>
+        <v>-0.1928</v>
       </c>
       <c r="T26" t="n">
         <v>0.2326</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4649</v>
+        <v>-0.4253</v>
       </c>
       <c r="V26" t="n">
         <v>-1.8894</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.828</v>
+        <v>-3.0601</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.4295</v>
+        <v>-0.9399</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.3985</v>
+        <v>-2.1202</v>
       </c>
       <c r="G27" t="n">
         <v>-3.0438</v>
@@ -2560,13 +2560,13 @@
         <v>0.9264</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.4698</v>
+        <v>0.2981</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.046</v>
+        <v>0.4436</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.4238</v>
+        <v>-0.1455</v>
       </c>
       <c r="V27" t="n">
         <v>-0.3144</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-7.0933</v>
+        <v>-5.8346</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.1286</v>
+        <v>-1.3452</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.9647</v>
+        <v>-4.4894</v>
       </c>
       <c r="G28" t="n">
         <v>-3.878</v>
@@ -2638,13 +2638,13 @@
         <v>1.4823</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.9178</v>
+        <v>-0.6591</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.3743</v>
+        <v>0.4091</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.5435</v>
+        <v>-1.0682</v>
       </c>
       <c r="V28" t="n">
         <v>-0.0005</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>9.249599999999997</v>
+        <v>10.5554</v>
       </c>
       <c r="E29" t="n">
-        <v>19.1615</v>
+        <v>19.1613</v>
       </c>
       <c r="F29" t="n">
-        <v>-9.911999999999999</v>
+        <v>-8.606199999999999</v>
       </c>
       <c r="G29" t="n">
         <v>1.3264</v>
@@ -2707,7 +2707,7 @@
         <v>-12.7084</v>
       </c>
       <c r="P29" t="n">
-        <v>4.631999999999999</v>
+        <v>4.632</v>
       </c>
       <c r="Q29" t="n">
         <v>-10.1908</v>
@@ -2716,13 +2716,13 @@
         <v>14.8227</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.4849999999999994</v>
+        <v>0.8207</v>
       </c>
       <c r="T29" t="n">
-        <v>4.091299999999999</v>
+        <v>4.0915</v>
       </c>
       <c r="U29" t="n">
-        <v>-4.5764</v>
+        <v>-3.270700000000001</v>
       </c>
       <c r="V29" t="n">
         <v>3.776</v>
